--- a/26年09-12月シフト.xlsx
+++ b/26年09-12月シフト.xlsx
@@ -800,9 +800,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
@@ -810,9 +810,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">
@@ -859,14 +859,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S3" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S3" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U3" s="8" t="inlineStr">
@@ -888,9 +888,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z3" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z3" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA3" s="8" t="inlineStr">
@@ -913,9 +913,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF3" s="8" t="inlineStr">
@@ -1018,14 +1018,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S4" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T4" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U4" s="12" t="inlineStr">
@@ -1057,9 +1057,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB4" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC4" s="12" t="inlineStr">
@@ -1077,9 +1077,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AF4" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AG4" s="11" t="inlineStr">
@@ -1202,9 +1202,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA5" s="8" t="inlineStr">
@@ -1212,14 +1212,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB5" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AC5" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB5" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AC5" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD5" s="8" t="inlineStr">
@@ -1232,9 +1232,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AF5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AG5" s="8" t="inlineStr">
@@ -1273,9 +1273,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -1283,9 +1283,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr">
@@ -1376,9 +1376,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC6" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD6" s="11" t="inlineStr">
@@ -1386,9 +1386,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE6" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF6" s="12" t="inlineStr">
@@ -1814,9 +1814,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA9" s="8" t="inlineStr">
@@ -1824,9 +1824,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC9" s="8" t="inlineStr">
@@ -1885,9 +1885,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
@@ -1895,9 +1895,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr">
@@ -1944,14 +1944,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T10" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S10" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U10" s="12" t="inlineStr">
@@ -1973,9 +1973,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z10" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA10" s="12" t="inlineStr">
@@ -1998,9 +1998,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE10" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF10" s="12" t="inlineStr">
@@ -2099,14 +2099,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U11" s="8" t="inlineStr">
@@ -2138,9 +2138,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC11" s="8" t="inlineStr">
@@ -2158,9 +2158,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AF11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AG11" s="11" t="inlineStr">
@@ -2298,9 +2298,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD12" s="8" t="inlineStr">
@@ -2313,9 +2313,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AF12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AG12" s="8" t="inlineStr">
@@ -2354,9 +2354,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -2364,9 +2364,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I13" s="12" t="inlineStr">
@@ -2457,9 +2457,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC13" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD13" s="11" t="inlineStr">
@@ -2467,9 +2467,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE13" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF13" s="12" t="inlineStr">
@@ -2899,9 +2899,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z16" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA16" s="8" t="inlineStr">
@@ -2909,9 +2909,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB16" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC16" s="8" t="inlineStr">
@@ -2966,9 +2966,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
@@ -2976,9 +2976,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
@@ -3025,14 +3025,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S17" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U17" s="8" t="inlineStr">
@@ -3054,9 +3054,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z17" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA17" s="8" t="inlineStr">
@@ -3079,9 +3079,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE17" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF17" s="8" t="inlineStr">
@@ -3184,14 +3184,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S18" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T18" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U18" s="12" t="inlineStr">
@@ -3223,9 +3223,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB18" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC18" s="12" t="inlineStr">
@@ -3243,9 +3243,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AF18" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AG18" s="11" t="inlineStr">
@@ -3383,9 +3383,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD19" s="8" t="inlineStr">
@@ -3398,9 +3398,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AF19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AG19" s="8" t="inlineStr">
@@ -3435,9 +3435,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
@@ -3445,9 +3445,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
@@ -3538,9 +3538,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC20" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD20" s="11" t="inlineStr">
@@ -3548,9 +3548,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE20" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE20" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF20" s="8" t="inlineStr">
@@ -4432,9 +4432,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD26" s="8" t="inlineStr">
@@ -4447,9 +4447,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AF26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AG26" s="8" t="inlineStr">
@@ -4488,9 +4488,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -4498,9 +4498,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="H27" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
@@ -4591,9 +4591,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC27" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD27" s="11" t="inlineStr">
@@ -4601,9 +4601,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE27" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF27" s="12" t="inlineStr">
@@ -5005,14 +5005,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="T30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V30" s="8">
@@ -5029,9 +5029,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA30" s="8" t="inlineStr">
@@ -5039,9 +5039,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AC30" s="8" t="inlineStr">
@@ -5096,9 +5096,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
@@ -5106,9 +5106,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
@@ -5155,14 +5155,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S31" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S31" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T31" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U31" s="8" t="inlineStr">
@@ -5184,9 +5184,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z31" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z31" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA31" s="8" t="inlineStr">
@@ -5209,9 +5209,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE31" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE31" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF31" s="8" t="inlineStr">
@@ -5310,9 +5310,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T32" s="11" t="inlineStr">
@@ -5320,9 +5320,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="U32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V32" s="8">
@@ -5349,9 +5349,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC32" s="8" t="inlineStr">
@@ -5369,9 +5369,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AF32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AG32" s="11" t="inlineStr">
@@ -5697,117 +5697,117 @@
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
           <t>金</t>
         </is>
       </c>
-      <c r="G36" s="17" t="inlineStr">
+      <c r="H36" s="17" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="H36" s="17" t="inlineStr">
+      <c r="I36" s="17" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="J36" s="17" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="K36" s="17" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="L36" s="17" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="I36" s="17" t="inlineStr">
+      <c r="M36" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="N36" s="17" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="Q36" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="R36" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="S36" s="17" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="T36" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="U36" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="X36" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y36" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z36" s="17" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="AA36" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="AB36" s="17" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="AC36" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="AD36" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="AE36" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="AF36" s="17" t="inlineStr">
         <is>
           <t>木</t>
-        </is>
-      </c>
-      <c r="J36" s="17" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="K36" s="17" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="L36" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="M36" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="N36" s="17" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="Q36" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="R36" s="17" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="S36" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="T36" s="17" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="U36" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="X36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z36" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="AA36" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="AB36" s="17" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="AC36" s="17" t="inlineStr">
-        <is>
-          <t>木</t>
-        </is>
-      </c>
-      <c r="AD36" s="17" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="AE36" s="17" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="AF36" s="17" t="inlineStr">
-        <is>
-          <t>水</t>
         </is>
       </c>
       <c r="AG36" s="17" t="inlineStr">
@@ -6059,9 +6059,9 @@
       </c>
       <c r="C3" s="9" t="inlineStr"/>
       <c r="D3" s="10" t="inlineStr"/>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
@@ -6123,14 +6123,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="S3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T3" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U3" s="8" t="inlineStr">
@@ -6167,9 +6167,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD3" s="11" t="inlineStr">
@@ -6177,9 +6177,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE3" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE3" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF3" s="8" t="inlineStr">
@@ -6283,14 +6283,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V4" s="8">
@@ -6317,14 +6317,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AC4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AC4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD4" s="8" t="inlineStr">
@@ -6332,14 +6332,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AF4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="AF4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AG4" s="8" t="inlineStr">
@@ -6374,9 +6374,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
@@ -6384,9 +6384,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
@@ -6423,9 +6423,9 @@
         <f>COUNTIF(E5:N5, "○")</f>
         <v/>
       </c>
-      <c r="Q5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Q5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="R5" s="8" t="inlineStr">
@@ -6438,9 +6438,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T5" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U5" s="11" t="inlineStr">
@@ -6671,9 +6671,9 @@
       </c>
       <c r="C7" s="9" t="inlineStr"/>
       <c r="D7" s="10" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -6691,9 +6691,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
@@ -6735,9 +6735,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
@@ -6745,9 +6745,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V7" s="8">
@@ -6764,9 +6764,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA7" s="8" t="inlineStr">
@@ -6774,9 +6774,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC7" s="8" t="inlineStr">
@@ -6890,14 +6890,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S8" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U8" s="8" t="inlineStr">
@@ -6919,9 +6919,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z8" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA8" s="8" t="inlineStr">
@@ -7050,14 +7050,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V9" s="8">
@@ -7136,9 +7136,9 @@
       </c>
       <c r="C10" s="9" t="inlineStr"/>
       <c r="D10" s="10" t="inlineStr"/>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -7156,9 +7156,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -7200,14 +7200,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="S10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U10" s="8" t="inlineStr">
@@ -7244,9 +7244,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD10" s="11" t="inlineStr">
@@ -7254,9 +7254,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE10" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF10" s="8" t="inlineStr">
@@ -7359,14 +7359,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T11" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S11" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U11" s="12" t="inlineStr">
@@ -7398,14 +7398,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AC11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB11" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AC11" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD11" s="12" t="inlineStr">
@@ -7413,9 +7413,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE11" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF11" s="12" t="inlineStr">
@@ -7450,9 +7450,9 @@
       </c>
       <c r="C12" s="9" t="inlineStr"/>
       <c r="D12" s="10" t="inlineStr"/>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -7475,9 +7475,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="K12" s="8" t="inlineStr">
@@ -7920,9 +7920,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="K15" s="8" t="inlineStr">
@@ -7959,14 +7959,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S15" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U15" s="8" t="inlineStr">
@@ -8118,14 +8118,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S16" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T16" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T16" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U16" s="12" t="inlineStr">
@@ -8147,9 +8147,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z16" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z16" s="8" t="inlineStr">
+        <is>
+          <t>特有</t>
         </is>
       </c>
       <c r="AA16" s="12" t="inlineStr">
@@ -8157,9 +8157,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB16" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB16" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC16" s="12" t="inlineStr">
@@ -8209,9 +8209,9 @@
       </c>
       <c r="C17" s="9" t="inlineStr"/>
       <c r="D17" s="10" t="inlineStr"/>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -8273,14 +8273,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="S17" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U17" s="8" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="Z17" s="8" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>特有</t>
         </is>
       </c>
       <c r="AA17" s="8" t="inlineStr">
@@ -8317,9 +8317,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC17" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD17" s="11" t="inlineStr">
@@ -8327,9 +8327,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE17" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF17" s="8" t="inlineStr">
@@ -8432,14 +8432,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T18" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S18" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U18" s="12" t="inlineStr">
@@ -8461,9 +8461,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z18" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA18" s="12" t="inlineStr">
@@ -8471,14 +8471,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AC18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB18" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AC18" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD18" s="12" t="inlineStr">
@@ -8486,9 +8486,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE18" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF18" s="12" t="inlineStr">
@@ -8523,9 +8523,9 @@
       </c>
       <c r="C19" s="9" t="inlineStr"/>
       <c r="D19" s="10" t="inlineStr"/>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -8548,9 +8548,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
@@ -8821,9 +8821,9 @@
       </c>
       <c r="C21" s="9" t="inlineStr"/>
       <c r="D21" s="10" t="inlineStr"/>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -8841,9 +8841,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
@@ -8914,9 +8914,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA21" s="8" t="inlineStr">
@@ -8924,9 +8924,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC21" s="8" t="inlineStr">
@@ -9001,9 +9001,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="K22" s="8" t="inlineStr">
@@ -9040,14 +9040,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S22" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U22" s="8" t="inlineStr">
@@ -9069,9 +9069,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z22" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA22" s="8" t="inlineStr">
@@ -9195,14 +9195,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S23" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T23" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S23" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U23" s="8" t="inlineStr">
@@ -9286,9 +9286,9 @@
       </c>
       <c r="C24" s="9" t="inlineStr"/>
       <c r="D24" s="10" t="inlineStr"/>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -9306,9 +9306,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
@@ -9350,14 +9350,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="S24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U24" s="8" t="inlineStr">
@@ -9394,9 +9394,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD24" s="11" t="inlineStr">
@@ -9404,9 +9404,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF24" s="8" t="inlineStr">
@@ -9509,14 +9509,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T25" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S25" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U25" s="12" t="inlineStr">
@@ -9548,14 +9548,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AC25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AB25" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AC25" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD25" s="12" t="inlineStr">
@@ -9563,9 +9563,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE25" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF25" s="12" t="inlineStr">
@@ -9615,9 +9615,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
@@ -9645,9 +9645,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="N26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O26" s="8">
@@ -9664,14 +9664,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U26" s="11" t="inlineStr">
@@ -9898,9 +9898,9 @@
       </c>
       <c r="C28" s="9" t="inlineStr"/>
       <c r="D28" s="10" t="inlineStr"/>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -9918,9 +9918,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J28" s="11" t="inlineStr">
@@ -9991,9 +9991,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA28" s="8" t="inlineStr">
@@ -10001,9 +10001,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC28" s="8" t="inlineStr">
@@ -10021,9 +10021,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AF28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AF28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AG28" s="8" t="inlineStr">
@@ -10281,14 +10281,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="T30" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U30" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V30" s="8">
@@ -10367,9 +10367,9 @@
       </c>
       <c r="C31" s="9" t="inlineStr"/>
       <c r="D31" s="10" t="inlineStr"/>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -10387,9 +10387,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J31" s="8" t="inlineStr">
@@ -10431,14 +10431,14 @@
           <t>公</t>
         </is>
       </c>
-      <c r="S31" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T31" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S31" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U31" s="8" t="inlineStr">
@@ -10475,9 +10475,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC31" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AC31" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD31" s="11" t="inlineStr">
@@ -10485,9 +10485,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE31" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE31" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF31" s="8" t="inlineStr">
@@ -10586,14 +10586,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U32" s="11" t="inlineStr">
@@ -10630,9 +10630,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AC32" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC32" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD32" s="8" t="inlineStr">
@@ -10640,9 +10640,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE32" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE32" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF32" s="8" t="inlineStr">
@@ -10682,9 +10682,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -10722,18 +10722,18 @@
           <t>公</t>
         </is>
       </c>
-      <c r="N33" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N33" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O33" s="8">
         <f>COUNTIF(E33:N33, "○")</f>
         <v/>
       </c>
-      <c r="Q33" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Q33" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="R33" s="8" t="inlineStr">
@@ -10746,9 +10746,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T33" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U33" s="11" t="inlineStr">
@@ -10984,7 +10984,7 @@
         <v>13</v>
       </c>
       <c r="Z35" s="17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA35" s="17" t="n">
         <v>21</v>
@@ -11123,117 +11123,117 @@
       </c>
       <c r="E37" s="17" t="inlineStr">
         <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="H37" s="17" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="I37" s="17" t="inlineStr">
+        <is>
           <t>木</t>
         </is>
       </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="G37" s="17" t="inlineStr">
+      <c r="J37" s="17" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="K37" s="17" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="H37" s="17" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="I37" s="17" t="inlineStr">
+      <c r="L37" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="M37" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="N37" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="Q37" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="R37" s="17" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="S37" s="17" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="T37" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="U37" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="X37" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y37" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z37" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="AA37" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="AB37" s="17" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="J37" s="17" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="K37" s="17" t="inlineStr">
+      <c r="AC37" s="17" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="AD37" s="17" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="AE37" s="17" t="inlineStr">
         <is>
           <t>金</t>
-        </is>
-      </c>
-      <c r="L37" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="M37" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="N37" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="Q37" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="R37" s="17" t="inlineStr">
-        <is>
-          <t>木</t>
-        </is>
-      </c>
-      <c r="S37" s="17" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="T37" s="17" t="inlineStr">
-        <is>
-          <t>木</t>
-        </is>
-      </c>
-      <c r="U37" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="X37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z37" s="17" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="AA37" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="AB37" s="17" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="AC37" s="17" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="AD37" s="17" t="inlineStr">
-        <is>
-          <t>木</t>
-        </is>
-      </c>
-      <c r="AE37" s="17" t="inlineStr">
-        <is>
-          <t>木</t>
         </is>
       </c>
       <c r="AF37" s="17" t="inlineStr">
@@ -11633,9 +11633,9 @@
       </c>
       <c r="C4" s="9" t="inlineStr"/>
       <c r="D4" s="10" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -11653,9 +11653,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="J4" s="11" t="inlineStr">
@@ -11687,9 +11687,9 @@
         <f>COUNTIF(E4:N4, "○")</f>
         <v/>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Q4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="R4" s="8" t="inlineStr">
@@ -11697,14 +11697,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U4" s="8" t="inlineStr">
@@ -11726,9 +11726,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA4" s="8" t="inlineStr">
@@ -11736,9 +11736,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB4" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC4" s="8" t="inlineStr">
@@ -11949,9 +11949,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
@@ -11984,18 +11984,18 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N6" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O6" s="8">
         <f>COUNTIF(E6:N6, "○")</f>
         <v/>
       </c>
-      <c r="Q6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Q6" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="R6" s="12" t="inlineStr">
@@ -12008,9 +12008,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T6" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U6" s="12" t="inlineStr">
@@ -12042,14 +12042,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AC6" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB6" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AC6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD6" s="12" t="inlineStr">
@@ -12099,14 +12099,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
@@ -12158,9 +12158,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
@@ -12168,9 +12168,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V7" s="8">
@@ -12202,9 +12202,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC7" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD7" s="8" t="inlineStr">
@@ -12212,9 +12212,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE7" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF7" s="11" t="inlineStr">
@@ -12258,9 +12258,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
@@ -12298,9 +12298,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N8" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O8" s="8">
@@ -12346,9 +12346,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z8" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z8" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA8" s="12" t="inlineStr">
@@ -12371,9 +12371,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE8" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE8" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF8" s="12" t="inlineStr">
@@ -12408,9 +12408,9 @@
       </c>
       <c r="C9" s="9" t="inlineStr"/>
       <c r="D9" s="10" t="inlineStr"/>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -12428,9 +12428,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -12472,9 +12472,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S9" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
@@ -12770,9 +12770,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T11" s="11" t="inlineStr">
@@ -12780,9 +12780,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="U11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V11" s="8">
@@ -12925,14 +12925,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U12" s="8" t="inlineStr">
@@ -12954,9 +12954,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA12" s="8" t="inlineStr">
@@ -12964,9 +12964,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC12" s="8" t="inlineStr">
@@ -13026,9 +13026,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
@@ -13061,9 +13061,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N13" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O13" s="8">
@@ -13080,14 +13080,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S13" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U13" s="8" t="inlineStr">
@@ -13119,14 +13119,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AC13" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB13" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AC13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD13" s="8" t="inlineStr">
@@ -13176,14 +13176,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -13235,9 +13235,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S14" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S14" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
@@ -13245,9 +13245,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U14" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V14" s="8">
@@ -13279,9 +13279,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC14" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC14" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD14" s="8" t="inlineStr">
@@ -13289,9 +13289,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE14" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE14" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF14" s="11" t="inlineStr">
@@ -13335,9 +13335,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
@@ -13375,9 +13375,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N15" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O15" s="8">
@@ -13423,9 +13423,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z15" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z15" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA15" s="12" t="inlineStr">
@@ -13448,9 +13448,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE15" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE15" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF15" s="12" t="inlineStr">
@@ -13847,9 +13847,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T18" s="11" t="inlineStr">
@@ -13857,9 +13857,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="U18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V18" s="8">
@@ -14002,14 +14002,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U19" s="8" t="inlineStr">
@@ -14031,9 +14031,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA19" s="8" t="inlineStr">
@@ -14041,9 +14041,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC19" s="8" t="inlineStr">
@@ -14107,9 +14107,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
@@ -14142,9 +14142,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N20" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O20" s="8">
@@ -14161,14 +14161,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S20" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="T20" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S20" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U20" s="12" t="inlineStr">
@@ -14200,14 +14200,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB20" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AC20" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB20" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AC20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD20" s="12" t="inlineStr">
@@ -14257,14 +14257,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -14316,9 +14316,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -14326,9 +14326,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V21" s="8">
@@ -14360,9 +14360,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC21" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD21" s="8" t="inlineStr">
@@ -14370,9 +14370,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE21" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE21" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF21" s="11" t="inlineStr">
@@ -14416,9 +14416,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
@@ -14456,9 +14456,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N22" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O22" s="8">
@@ -14504,9 +14504,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z22" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z22" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA22" s="12" t="inlineStr">
@@ -14529,9 +14529,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE22" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE22" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF22" s="12" t="inlineStr">
@@ -15075,14 +15075,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U26" s="8" t="inlineStr">
@@ -15104,9 +15104,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="Z26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="Z26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AA26" s="8" t="inlineStr">
@@ -15114,9 +15114,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC26" s="8" t="inlineStr">
@@ -15176,9 +15176,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -15211,9 +15211,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O27" s="8">
@@ -15235,14 +15235,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V27" s="8">
@@ -15269,14 +15269,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AC27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AC27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD27" s="8" t="inlineStr">
@@ -15326,14 +15326,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -15385,9 +15385,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="S28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
@@ -15395,9 +15395,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="U28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V28" s="8">
@@ -15429,9 +15429,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC28" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC28" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD28" s="8" t="inlineStr">
@@ -15439,9 +15439,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE28" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE28" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF28" s="11" t="inlineStr">
@@ -15481,9 +15481,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
@@ -15521,9 +15521,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N29" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O29" s="8">
@@ -15540,9 +15540,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="S29" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="S29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
@@ -15550,9 +15550,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V29" s="8">
@@ -15569,9 +15569,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Z29" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Z29" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AA29" s="8" t="inlineStr">
@@ -15594,9 +15594,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE29" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE29" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF29" s="8" t="inlineStr">
@@ -16380,112 +16380,112 @@
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
           <t>木</t>
         </is>
       </c>
-      <c r="G36" s="17" t="inlineStr">
+      <c r="H36" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="I36" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="J36" s="17" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="K36" s="17" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="H36" s="17" t="inlineStr">
+      <c r="L36" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="M36" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="N36" s="17" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="Q36" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="R36" s="17" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="I36" s="17" t="inlineStr">
+      <c r="S36" s="17" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="T36" s="17" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="U36" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="X36" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y36" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z36" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="AA36" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="AB36" s="17" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="J36" s="17" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="K36" s="17" t="inlineStr">
+      <c r="AC36" s="17" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="L36" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="M36" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="N36" s="17" t="inlineStr">
+      <c r="AD36" s="17" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="Q36" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="R36" s="17" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="S36" s="17" t="inlineStr">
+      <c r="AE36" s="17" t="inlineStr">
         <is>
           <t>木</t>
-        </is>
-      </c>
-      <c r="T36" s="17" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="U36" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="X36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z36" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="AA36" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="AB36" s="17" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="AC36" s="17" t="inlineStr">
-        <is>
-          <t>木</t>
-        </is>
-      </c>
-      <c r="AD36" s="17" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="AE36" s="17" t="inlineStr">
-        <is>
-          <t>金</t>
         </is>
       </c>
       <c r="AF36" s="17" t="inlineStr">
@@ -16845,14 +16845,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB3" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AC3" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB3" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AC3" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD3" s="8" t="inlineStr">
@@ -16906,9 +16906,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G4" s="12" t="inlineStr">
@@ -16946,9 +16946,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O4" s="8">
@@ -16970,9 +16970,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T4" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T4" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="U4" s="12" t="inlineStr">
@@ -17125,9 +17125,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="U5" s="11" t="inlineStr">
@@ -17159,9 +17159,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB5" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB5" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC5" s="8" t="inlineStr">
@@ -17174,9 +17174,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE5" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE5" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF5" s="8" t="inlineStr">
@@ -17220,9 +17220,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -17260,9 +17260,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N6" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O6" s="8">
@@ -17323,9 +17323,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC6" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC6" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD6" s="12" t="inlineStr">
@@ -17333,9 +17333,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE6" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE6" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF6" s="12" t="inlineStr">
@@ -17926,14 +17926,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB10" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AC10" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB10" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AC10" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD10" s="8" t="inlineStr">
@@ -17983,9 +17983,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -18023,9 +18023,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O11" s="8">
@@ -18047,14 +18047,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T11" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U11" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V11" s="8">
@@ -18202,14 +18202,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V12" s="8">
@@ -18236,9 +18236,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB12" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB12" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC12" s="8" t="inlineStr">
@@ -18251,9 +18251,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE12" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE12" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF12" s="8" t="inlineStr">
@@ -18297,9 +18297,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -18337,9 +18337,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N13" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O13" s="8">
@@ -18400,9 +18400,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC13" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC13" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD13" s="12" t="inlineStr">
@@ -18410,9 +18410,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE13" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE13" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF13" s="12" t="inlineStr">
@@ -19007,14 +19007,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB17" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AC17" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB17" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AC17" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD17" s="12" t="inlineStr">
@@ -19064,9 +19064,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
@@ -19104,9 +19104,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O18" s="8">
@@ -19128,14 +19128,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T18" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U18" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V18" s="8">
@@ -19283,14 +19283,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V19" s="8">
@@ -19317,9 +19317,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB19" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB19" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC19" s="8" t="inlineStr">
@@ -19332,9 +19332,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE19" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF19" s="8" t="inlineStr">
@@ -19378,9 +19378,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
@@ -19418,9 +19418,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N20" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O20" s="8">
@@ -19481,9 +19481,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC20" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC20" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD20" s="12" t="inlineStr">
@@ -19491,9 +19491,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE20" s="12" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE20" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF20" s="12" t="inlineStr">
@@ -20084,14 +20084,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB24" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="AC24" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB24" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AC24" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AD24" s="8" t="inlineStr">
@@ -20141,9 +20141,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
@@ -20181,9 +20181,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="N25" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="O25" s="8">
@@ -20205,14 +20205,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T25" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U25" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="V25" s="8">
@@ -20360,14 +20360,14 @@
           <t>○</t>
         </is>
       </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="T26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="V26" s="8">
@@ -20394,9 +20394,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AB26" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AB26" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AC26" s="8" t="inlineStr">
@@ -20409,9 +20409,9 @@
           <t>公</t>
         </is>
       </c>
-      <c r="AE26" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AE26" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AF26" s="8" t="inlineStr">
@@ -20451,9 +20451,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -20491,9 +20491,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="N27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="N27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="O27" s="8">
@@ -20554,9 +20554,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AC27" s="11" t="inlineStr">
-        <is>
-          <t>公</t>
+      <c r="AC27" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="AD27" s="8" t="inlineStr">
@@ -20564,9 +20564,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AE27" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="AE27" s="11" t="inlineStr">
+        <is>
+          <t>公</t>
         </is>
       </c>
       <c r="AF27" s="8" t="inlineStr">
@@ -21153,7 +21153,7 @@
       </c>
       <c r="Z31" s="8" t="inlineStr">
         <is>
-          <t>特有</t>
+          <t>○</t>
         </is>
       </c>
       <c r="AA31" s="8" t="inlineStr">
@@ -21312,7 +21312,7 @@
       </c>
       <c r="Z32" s="8" t="inlineStr">
         <is>
-          <t>特有</t>
+          <t>○</t>
         </is>
       </c>
       <c r="AA32" s="8" t="inlineStr">
@@ -21471,7 +21471,7 @@
       </c>
       <c r="Z33" s="8" t="inlineStr">
         <is>
-          <t>特有</t>
+          <t>○</t>
         </is>
       </c>
       <c r="AA33" s="8" t="inlineStr">
@@ -21683,7 +21683,7 @@
         <v>12</v>
       </c>
       <c r="Z35" s="17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA35" s="17" t="n">
         <v>20</v>
@@ -21827,112 +21827,112 @@
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
           <t>金</t>
         </is>
       </c>
-      <c r="G37" s="17" t="inlineStr">
+      <c r="H37" s="17" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="I37" s="17" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="J37" s="17" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="K37" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="L37" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="M37" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="N37" s="17" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="H37" s="17" t="inlineStr">
+      <c r="Q37" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="R37" s="17" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="I37" s="17" t="inlineStr">
+      <c r="S37" s="17" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="T37" s="17" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="J37" s="17" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="K37" s="17" t="inlineStr">
+      <c r="U37" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="X37" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y37" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z37" s="17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="AA37" s="17" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="AB37" s="17" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="AC37" s="17" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="L37" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="M37" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="N37" s="17" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="Q37" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="R37" s="17" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="S37" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="T37" s="17" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="U37" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="X37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z37" s="17" t="inlineStr">
+      <c r="AD37" s="17" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="AE37" s="17" t="inlineStr">
         <is>
           <t>金</t>
-        </is>
-      </c>
-      <c r="AA37" s="17" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="AB37" s="17" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="AC37" s="17" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="AD37" s="17" t="inlineStr">
-        <is>
-          <t>木</t>
-        </is>
-      </c>
-      <c r="AE37" s="17" t="inlineStr">
-        <is>
-          <t>木</t>
         </is>
       </c>
       <c r="AF37" s="17" t="inlineStr">
